--- a/StructureDefinition-open-elis-specimen.xlsx
+++ b/StructureDefinition-open-elis-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T18:31:44+00:00</t>
+    <t>2025-09-03T10:18:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-open-elis-specimen.xlsx
+++ b/StructureDefinition-open-elis-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T10:18:48+00:00</t>
+    <t>2026-03-23T16:02:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -352,7 +352,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -590,7 +590,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -617,7 +617,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/sampleItem_uuid</t>
+    <t>http://openelis-global.org/sampleItem_uuid</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -690,7 +690,7 @@
     <t>Specimen.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1046,7 +1046,7 @@
     <t>Specimen.parent</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1138,7 +1138,7 @@
     <t>Specimen.collection.collector</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -1204,7 +1204,7 @@
     <t>Specimen.collection.quantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1232,7 +1232,7 @@
     <t>The  technique that is used to perform the procedure.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/specimen-collection-method</t>
+    <t>http://hl7.org/fhir/ValueSet/specimen-collection-method|4.0.1</t>
   </si>
   <si>
     <t>.methodCode</t>
@@ -1256,7 +1256,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>.targetSiteCode</t>
@@ -1338,13 +1338,13 @@
     <t>Type indicating the technique used to process the specimen.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/specimen-processing-procedure</t>
+    <t>http://hl7.org/fhir/ValueSet/specimen-processing-procedure|4.0.1</t>
   </si>
   <si>
     <t>Specimen.processing.additive</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Substance)
+    <t xml:space="preserve">Reference(Substance|4.0.1)
 </t>
   </si>
   <si>
@@ -1430,7 +1430,7 @@
     <t>Type of specimen container.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/specimen-container-type</t>
+    <t>http://hl7.org/fhir/ValueSet/specimen-container-type|4.0.1</t>
   </si>
   <si>
     <t>SPM-27</t>
@@ -1470,7 +1470,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Substance)</t>
+Reference(Substance|4.0.1)</t>
   </si>
   <si>
     <t>Additive associated with container</t>
@@ -1848,7 +1848,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="47.75" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.27734375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-open-elis-specimen.xlsx
+++ b/StructureDefinition-open-elis-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T16:02:58+00:00</t>
+    <t>2026-05-11T11:15:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-open-elis-specimen.xlsx
+++ b/StructureDefinition-open-elis-specimen.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2827" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2827" uniqueCount="495">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T11:15:58+00:00</t>
+    <t>2026-05-11T15:58:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1148,6 +1148,9 @@
     <t>Person who collected the specimen.</t>
   </si>
   <si>
+    <t>SampleItem.collector</t>
+  </si>
+  <si>
     <t>.participation[typeCode=PFM].role</t>
   </si>
   <si>
@@ -1259,6 +1262,9 @@
     <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
+    <t>SampleItem.sourceOfSample</t>
+  </si>
+  <si>
     <t>.targetSiteCode</t>
   </si>
   <si>
@@ -1458,6 +1464,9 @@
   </si>
   <si>
     <t>The quantity of specimen in the container; may be volume, dimensions, or other appropriate measurements, depending on the specimen type.</t>
+  </si>
+  <si>
+    <t>SampleItem.quantity</t>
   </si>
   <si>
     <t>.playedRole[classCode=CONT].quantity</t>
@@ -7668,24 +7677,24 @@
         <v>96</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>17</v>
+        <v>367</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7711,10 +7720,10 @@
         <v>328</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7753,17 +7762,17 @@
         <v>17</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AC52" s="2"/>
       <c r="AD52" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>74</v>
@@ -7781,24 +7790,24 @@
         <v>17</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>17</v>
@@ -7823,10 +7832,10 @@
         <v>328</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7877,7 +7886,7 @@
         <v>17</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>74</v>
@@ -7895,21 +7904,21 @@
         <v>17</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7932,13 +7941,13 @@
         <v>84</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7989,7 +7998,7 @@
         <v>17</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>74</v>
@@ -8010,7 +8019,7 @@
         <v>17</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>17</v>
@@ -8018,10 +8027,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8044,13 +8053,13 @@
         <v>17</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8101,7 +8110,7 @@
         <v>17</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>74</v>
@@ -8119,21 +8128,21 @@
         <v>17</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8159,10 +8168,10 @@
         <v>178</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8192,10 +8201,10 @@
         <v>252</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>17</v>
@@ -8213,7 +8222,7 @@
         <v>17</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>74</v>
@@ -8231,21 +8240,21 @@
         <v>17</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8271,13 +8280,13 @@
         <v>178</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8306,10 +8315,10 @@
         <v>252</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>17</v>
@@ -8327,7 +8336,7 @@
         <v>17</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>74</v>
@@ -8342,24 +8351,24 @@
         <v>96</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>17</v>
+        <v>404</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8382,19 +8391,19 @@
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>17</v>
@@ -8422,10 +8431,10 @@
         <v>183</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>17</v>
@@ -8443,7 +8452,7 @@
         <v>17</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>74</v>
@@ -8467,15 +8476,15 @@
         <v>17</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8501,10 +8510,10 @@
         <v>350</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8555,7 +8564,7 @@
         <v>17</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>74</v>
@@ -8573,7 +8582,7 @@
         <v>17</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>17</v>
@@ -8584,10 +8593,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8696,10 +8705,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8810,10 +8819,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8926,10 +8935,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8955,10 +8964,10 @@
         <v>154</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9009,7 +9018,7 @@
         <v>17</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>74</v>
@@ -9027,7 +9036,7 @@
         <v>17</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>17</v>
@@ -9038,10 +9047,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9067,10 +9076,10 @@
         <v>178</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9100,10 +9109,10 @@
         <v>252</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>17</v>
@@ -9121,7 +9130,7 @@
         <v>17</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>74</v>
@@ -9150,10 +9159,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9176,13 +9185,13 @@
         <v>17</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9233,7 +9242,7 @@
         <v>17</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>74</v>
@@ -9251,21 +9260,21 @@
         <v>17</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9288,13 +9297,13 @@
         <v>17</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9345,7 +9354,7 @@
         <v>17</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>74</v>
@@ -9363,7 +9372,7 @@
         <v>17</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>17</v>
@@ -9374,10 +9383,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9385,10 +9394,10 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>17</v>
@@ -9403,10 +9412,10 @@
         <v>350</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9457,7 +9466,7 @@
         <v>17</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>74</v>
@@ -9475,7 +9484,7 @@
         <v>17</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>17</v>
@@ -9486,10 +9495,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9598,10 +9607,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9712,10 +9721,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9828,10 +9837,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9857,10 +9866,10 @@
         <v>142</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9911,7 +9920,7 @@
         <v>17</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>74</v>
@@ -9935,15 +9944,15 @@
         <v>17</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9969,10 +9978,10 @@
         <v>154</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10023,7 +10032,7 @@
         <v>17</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>74</v>
@@ -10041,7 +10050,7 @@
         <v>17</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>17</v>
@@ -10052,10 +10061,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10081,10 +10090,10 @@
         <v>178</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10114,10 +10123,10 @@
         <v>252</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>17</v>
@@ -10135,7 +10144,7 @@
         <v>17</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>74</v>
@@ -10159,15 +10168,15 @@
         <v>17</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10190,13 +10199,13 @@
         <v>17</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10247,7 +10256,7 @@
         <v>17</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>74</v>
@@ -10265,21 +10274,21 @@
         <v>17</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10287,7 +10296,7 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>83</v>
@@ -10302,13 +10311,13 @@
         <v>17</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10359,7 +10368,7 @@
         <v>17</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>74</v>
@@ -10374,24 +10383,24 @@
         <v>96</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>17</v>
+        <v>471</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10414,13 +10423,13 @@
         <v>17</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10450,10 +10459,10 @@
         <v>252</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>17</v>
@@ -10471,7 +10480,7 @@
         <v>17</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>74</v>
@@ -10489,21 +10498,21 @@
         <v>17</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10529,16 +10538,16 @@
         <v>178</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>17</v>
@@ -10566,10 +10575,10 @@
         <v>183</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>17</v>
@@ -10587,7 +10596,7 @@
         <v>17</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>74</v>
@@ -10611,15 +10620,15 @@
         <v>17</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10642,13 +10651,13 @@
         <v>17</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="L78" t="s" s="2">
         <v>47</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10699,7 +10708,7 @@
         <v>17</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>74</v>
@@ -10717,13 +10726,13 @@
         <v>17</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
   </sheetData>

--- a/StructureDefinition-open-elis-specimen.xlsx
+++ b/StructureDefinition-open-elis-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:58:07+00:00</t>
+    <t>2026-05-12T16:33:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
